--- a/downloads/exercises/intermedio-m03-m03-l02-practice-01.xlsx
+++ b/downloads/exercises/intermedio-m03-m03-l02-practice-01.xlsx
@@ -348,7 +348,7 @@
       <x:c r="E5" s="14"/>
       <x:c r="F5" s="14"/>
       <x:c r="G5" t="str">
-        <x:v>Cambiar el año</x:v>
+        <x:v>Cambiar bloque central</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
